--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="48">
   <si>
     <t>No.</t>
   </si>
@@ -35,25 +35,43 @@
     <t>평균</t>
   </si>
   <si>
+    <t>393.0</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
     <t>429.6</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>4.3</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>356.3</t>
+  </si>
+  <si>
+    <t>785.9</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>7.9</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>03일</t>
   </si>
   <si>
     <t>04일</t>
@@ -448,16 +466,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="s" s="31">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s" s="32">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -465,19 +483,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -485,19 +503,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -505,19 +523,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -525,19 +543,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -545,19 +563,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -565,19 +583,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -585,19 +603,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -605,19 +623,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -625,19 +643,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -645,19 +663,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -665,19 +683,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -685,19 +703,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -705,19 +723,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -725,19 +743,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -745,19 +763,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -765,19 +783,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -785,19 +803,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -805,19 +823,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -825,19 +843,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -845,19 +863,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -865,19 +883,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -885,19 +903,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -905,19 +923,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -925,19 +943,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -945,19 +963,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -965,19 +983,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -985,19 +1003,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1005,19 +1023,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1025,19 +1043,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1045,19 +1063,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="52">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>393.0</t>
+    <t>372.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.9</t>
+    <t>3.7</t>
   </si>
   <si>
     <t>01일</t>
@@ -71,10 +71,22 @@
     <t>03일</t>
   </si>
   <si>
+    <t>332.1</t>
+  </si>
+  <si>
+    <t>1118.0</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>04일</t>
   </si>
   <si>
     <t>05일</t>
@@ -509,13 +521,13 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -523,19 +535,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -543,19 +555,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -563,19 +575,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -583,19 +595,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -603,19 +615,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -623,19 +635,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -643,19 +655,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -663,19 +675,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -683,19 +695,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -703,19 +715,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -723,19 +735,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -743,19 +755,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -763,19 +775,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -783,19 +795,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -803,19 +815,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -823,19 +835,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -843,19 +855,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -863,19 +875,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -883,19 +895,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -903,19 +915,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -923,19 +935,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -943,19 +955,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -963,19 +975,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -983,19 +995,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1003,19 +1015,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1023,19 +1035,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1043,19 +1055,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1063,19 +1075,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="55">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>372.7</t>
+    <t>385.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.7</t>
+    <t>3.9</t>
   </si>
   <si>
     <t>01일</t>
@@ -86,10 +86,19 @@
     <t>04일</t>
   </si>
   <si>
+    <t>425.8</t>
+  </si>
+  <si>
+    <t>1543.8</t>
+  </si>
+  <si>
+    <t>15.4</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>05일</t>
   </si>
   <si>
     <t>06일</t>
@@ -541,13 +550,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -555,19 +564,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -575,19 +584,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -595,19 +604,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -615,19 +624,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -635,19 +644,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -655,19 +664,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -675,19 +684,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -695,19 +704,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -715,19 +724,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -735,19 +744,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -755,19 +764,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -775,19 +784,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -795,19 +804,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -815,19 +824,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -835,19 +844,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -855,19 +864,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -875,19 +884,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -895,19 +904,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -915,19 +924,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -935,19 +944,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -955,19 +964,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -975,19 +984,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -995,19 +1004,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1015,19 +1024,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1035,19 +1044,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1055,19 +1064,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1075,19 +1084,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="59">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>385.9</t>
+    <t>345.2</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.9</t>
+    <t>3.5</t>
   </si>
   <si>
     <t>01일</t>
@@ -86,10 +86,10 @@
     <t>04일</t>
   </si>
   <si>
-    <t>425.8</t>
-  </si>
-  <si>
-    <t>1543.8</t>
+    <t>426.0</t>
+  </si>
+  <si>
+    <t>1544.0</t>
   </si>
   <si>
     <t>15.4</t>
@@ -98,10 +98,22 @@
     <t>05일</t>
   </si>
   <si>
+    <t>181.9</t>
+  </si>
+  <si>
+    <t>1725.9</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>17.3</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>06일</t>
   </si>
   <si>
     <t>07일</t>
@@ -570,13 +582,13 @@
         <v>28</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -584,19 +596,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -604,19 +616,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -624,19 +636,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -644,19 +656,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -664,19 +676,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -684,19 +696,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -704,19 +716,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -724,19 +736,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -744,19 +756,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -764,19 +776,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -784,19 +796,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -804,19 +816,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -824,19 +836,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -844,19 +856,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -864,19 +876,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -884,19 +896,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -904,19 +916,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -924,19 +936,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -944,19 +956,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -964,19 +976,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -984,19 +996,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1004,19 +1016,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1024,19 +1036,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1044,19 +1056,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1064,19 +1076,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1084,19 +1096,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="62">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>345.2</t>
+    <t>331.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.5</t>
+    <t>3.3</t>
   </si>
   <si>
     <t>01일</t>
@@ -77,9 +77,6 @@
     <t>1118.0</t>
   </si>
   <si>
-    <t>3.3</t>
-  </si>
-  <si>
     <t>11.2</t>
   </si>
   <si>
@@ -98,10 +95,10 @@
     <t>05일</t>
   </si>
   <si>
-    <t>181.9</t>
-  </si>
-  <si>
-    <t>1725.9</t>
+    <t>182.1</t>
+  </si>
+  <si>
+    <t>1726.1</t>
   </si>
   <si>
     <t>1.8</t>
@@ -113,10 +110,22 @@
     <t>06일</t>
   </si>
   <si>
+    <t>263.2</t>
+  </si>
+  <si>
+    <t>1989.3</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>19.9</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>07일</t>
   </si>
   <si>
     <t>08일</t>
@@ -545,10 +554,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s" s="34">
         <v>21</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -556,19 +565,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>23</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>24</v>
-      </c>
-      <c r="D6" t="s" s="37">
-        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
         <v>12</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -576,19 +585,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>27</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>28</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>29</v>
       </c>
-      <c r="E7" t="s" s="33">
+      <c r="F7" t="s" s="34">
         <v>30</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>31</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -596,19 +605,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>32</v>
-      </c>
-      <c r="C8" t="s" s="36">
-        <v>33</v>
       </c>
       <c r="D8" t="s" s="37">
         <v>33</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -616,19 +625,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -636,19 +645,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -656,19 +665,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -676,19 +685,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -696,19 +705,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -716,19 +725,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -736,19 +745,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -756,19 +765,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -776,19 +785,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -796,19 +805,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -816,19 +825,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -836,19 +845,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -856,19 +865,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -876,19 +885,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -896,19 +905,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -916,19 +925,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -936,19 +945,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -956,19 +965,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -976,19 +985,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -996,19 +1005,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1016,19 +1025,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1036,19 +1045,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1056,19 +1065,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1076,19 +1085,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1096,19 +1105,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="67">
   <si>
     <t>No.</t>
   </si>
@@ -35,48 +35,51 @@
     <t>평균</t>
   </si>
   <si>
-    <t>331.6</t>
+    <t>339.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>429.6</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>356.3</t>
+  </si>
+  <si>
+    <t>785.9</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>7.9</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>332.1</t>
+  </si>
+  <si>
+    <t>1118.0</t>
+  </si>
+  <si>
     <t>3.3</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>429.6</t>
-  </si>
-  <si>
-    <t>4.3</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>356.3</t>
-  </si>
-  <si>
-    <t>785.9</t>
-  </si>
-  <si>
-    <t>3.6</t>
-  </si>
-  <si>
-    <t>7.9</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>332.1</t>
-  </si>
-  <si>
-    <t>1118.0</t>
-  </si>
-  <si>
     <t>11.2</t>
   </si>
   <si>
@@ -125,10 +128,22 @@
     <t>07일</t>
   </si>
   <si>
+    <t>389.9</t>
+  </si>
+  <si>
+    <t>2379.2</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>23.8</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>08일</t>
   </si>
   <si>
     <t>09일</t>
@@ -554,10 +569,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -565,19 +580,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
         <v>12</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -585,19 +600,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -605,19 +620,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -625,19 +640,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -645,19 +660,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -665,19 +680,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -685,19 +700,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -705,19 +720,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -725,19 +740,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -745,19 +760,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -765,19 +780,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -785,19 +800,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -805,19 +820,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -825,19 +840,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -845,19 +860,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -865,19 +880,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -885,19 +900,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -905,19 +920,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -925,19 +940,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -945,19 +960,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -965,19 +980,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -985,19 +1000,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1005,19 +1020,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1025,19 +1040,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1045,19 +1060,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1065,19 +1080,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1085,19 +1100,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1105,19 +1120,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="71">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>339.9</t>
+    <t>308.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.4</t>
+    <t>3.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -143,10 +143,22 @@
     <t>08일</t>
   </si>
   <si>
+    <t>89.4</t>
+  </si>
+  <si>
+    <t>2468.6</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>24.7</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>09일</t>
   </si>
   <si>
     <t>10일</t>
@@ -666,13 +678,13 @@
         <v>43</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -680,19 +692,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -700,19 +712,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -720,19 +732,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -740,19 +752,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -760,19 +772,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -780,19 +792,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -800,19 +812,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -820,19 +832,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -840,19 +852,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -860,19 +872,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -880,19 +892,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -900,19 +912,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -920,19 +932,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -940,19 +952,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -960,19 +972,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -980,19 +992,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1000,19 +1012,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1020,19 +1032,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1040,19 +1052,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1060,19 +1072,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1080,19 +1092,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1100,19 +1112,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1120,19 +1132,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="74">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>308.6</t>
+    <t>284.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.1</t>
+    <t>2.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -158,10 +158,19 @@
     <t>09일</t>
   </si>
   <si>
+    <t>93.9</t>
+  </si>
+  <si>
+    <t>2562.5</t>
+  </si>
+  <si>
+    <t>25.6</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>10일</t>
   </si>
   <si>
     <t>11일</t>
@@ -698,13 +707,13 @@
         <v>48</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -712,19 +721,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -732,19 +741,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -752,19 +761,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -772,19 +781,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -792,19 +801,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -812,19 +821,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -832,19 +841,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -852,19 +861,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -872,19 +881,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -892,19 +901,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -912,19 +921,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -932,19 +941,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -952,19 +961,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -972,19 +981,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -992,19 +1001,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1012,19 +1021,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1032,19 +1041,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1052,19 +1061,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1072,19 +1081,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1092,19 +1101,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1112,19 +1121,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1132,19 +1141,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="86">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>284.7</t>
+    <t>313.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>2.8</t>
+    <t>3.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -170,16 +170,52 @@
     <t>10일</t>
   </si>
   <si>
+    <t>202.5</t>
+  </si>
+  <si>
+    <t>2765.0</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>27.6</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>483.3</t>
+  </si>
+  <si>
+    <t>3248.3</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>32.5</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>516.3</t>
+  </si>
+  <si>
+    <t>3764.6</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>37.6</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>13일</t>
   </si>
   <si>
     <t>14일</t>
@@ -727,13 +763,13 @@
         <v>52</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -741,19 +777,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -761,19 +797,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -781,19 +817,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -801,19 +837,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -821,19 +857,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -841,19 +877,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -861,19 +897,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -881,19 +917,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -901,19 +937,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -921,19 +957,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -941,19 +977,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -961,19 +997,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -981,19 +1017,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1001,19 +1037,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1021,19 +1057,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1041,19 +1077,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1061,19 +1097,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1081,19 +1117,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1101,19 +1137,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1121,19 +1157,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1141,19 +1177,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="90">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>313.7</t>
+    <t>321.3</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.1</t>
+    <t>3.2</t>
   </si>
   <si>
     <t>01일</t>
@@ -200,25 +200,37 @@
     <t>12일</t>
   </si>
   <si>
-    <t>516.3</t>
-  </si>
-  <si>
-    <t>3764.6</t>
+    <t>517.5</t>
+  </si>
+  <si>
+    <t>3765.8</t>
   </si>
   <si>
     <t>5.2</t>
   </si>
   <si>
-    <t>37.6</t>
+    <t>37.7</t>
   </si>
   <si>
     <t>13일</t>
   </si>
   <si>
+    <t>411.0</t>
+  </si>
+  <si>
+    <t>4176.8</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>41.8</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>14일</t>
   </si>
   <si>
     <t>15일</t>
@@ -823,13 +835,13 @@
         <v>67</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -837,19 +849,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -857,19 +869,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -877,19 +889,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -897,19 +909,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -917,19 +929,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -937,19 +949,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -957,19 +969,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -977,19 +989,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -997,19 +1009,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1017,19 +1029,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1037,19 +1049,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1057,19 +1069,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1077,19 +1089,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1097,19 +1109,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1117,19 +1129,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1137,19 +1149,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1157,19 +1169,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1177,19 +1189,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="94">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>321.3</t>
+    <t>317.5</t>
   </si>
   <si>
     <t>-</t>
@@ -230,10 +230,22 @@
     <t>14일</t>
   </si>
   <si>
+    <t>268.1</t>
+  </si>
+  <si>
+    <t>4444.9</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>44.4</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>15일</t>
   </si>
   <si>
     <t>16일</t>
@@ -855,13 +867,13 @@
         <v>72</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -869,19 +881,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -889,19 +901,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -909,19 +921,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -929,19 +941,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -949,19 +961,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -969,19 +981,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -989,19 +1001,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1009,19 +1021,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1029,19 +1041,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1049,19 +1061,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1069,19 +1081,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1089,19 +1101,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1109,19 +1121,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1129,19 +1141,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1149,19 +1161,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1169,19 +1181,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1189,19 +1201,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="97">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>317.5</t>
+    <t>314.3</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.2</t>
+    <t>3.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -245,10 +245,19 @@
     <t>15일</t>
   </si>
   <si>
+    <t>270.1</t>
+  </si>
+  <si>
+    <t>4715.0</t>
+  </si>
+  <si>
+    <t>47.1</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>16일</t>
   </si>
   <si>
     <t>17일</t>
@@ -887,13 +896,13 @@
         <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -901,19 +910,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -921,19 +930,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -941,19 +950,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -961,19 +970,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -981,19 +990,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1001,19 +1010,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1021,19 +1030,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1041,19 +1050,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1061,19 +1070,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1081,19 +1090,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1101,19 +1110,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1121,19 +1130,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1141,19 +1150,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1161,19 +1170,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1181,19 +1190,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1201,19 +1210,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="101">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>314.3</t>
+    <t>316.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.1</t>
+    <t>3.2</t>
   </si>
   <si>
     <t>01일</t>
@@ -245,22 +245,34 @@
     <t>15일</t>
   </si>
   <si>
-    <t>270.1</t>
-  </si>
-  <si>
-    <t>4715.0</t>
-  </si>
-  <si>
-    <t>47.1</t>
+    <t>270.7</t>
+  </si>
+  <si>
+    <t>4715.6</t>
+  </si>
+  <si>
+    <t>47.2</t>
   </si>
   <si>
     <t>16일</t>
   </si>
   <si>
+    <t>346.7</t>
+  </si>
+  <si>
+    <t>5062.3</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>50.6</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>17일</t>
   </si>
   <si>
     <t>18일</t>
@@ -916,13 +928,13 @@
         <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -930,19 +942,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -950,19 +962,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -970,19 +982,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -990,19 +1002,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1010,19 +1022,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1030,19 +1042,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1050,19 +1062,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1070,19 +1082,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1090,19 +1102,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1110,19 +1122,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1130,19 +1142,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1150,19 +1162,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1170,19 +1182,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1190,19 +1202,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1210,19 +1222,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="105">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>316.4</t>
+    <t>319.5</t>
   </si>
   <si>
     <t>-</t>
@@ -257,10 +257,10 @@
     <t>16일</t>
   </si>
   <si>
-    <t>346.7</t>
-  </si>
-  <si>
-    <t>5062.3</t>
+    <t>347.2</t>
+  </si>
+  <si>
+    <t>5062.8</t>
   </si>
   <si>
     <t>3.5</t>
@@ -272,10 +272,22 @@
     <t>17일</t>
   </si>
   <si>
+    <t>368.4</t>
+  </si>
+  <si>
+    <t>5431.2</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>54.3</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>18일</t>
   </si>
   <si>
     <t>19일</t>
@@ -948,13 +960,13 @@
         <v>86</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -962,19 +974,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -982,19 +994,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1002,19 +1014,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1022,19 +1034,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1042,19 +1054,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1062,19 +1074,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1082,19 +1094,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1102,19 +1114,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1122,19 +1134,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1142,19 +1154,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1162,19 +1174,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1182,19 +1194,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1202,19 +1214,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1222,19 +1234,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="109">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>319.5</t>
+    <t>308.2</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.2</t>
+    <t>3.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -272,10 +272,10 @@
     <t>17일</t>
   </si>
   <si>
-    <t>368.4</t>
-  </si>
-  <si>
-    <t>5431.2</t>
+    <t>368.7</t>
+  </si>
+  <si>
+    <t>5431.5</t>
   </si>
   <si>
     <t>3.7</t>
@@ -287,10 +287,22 @@
     <t>18일</t>
   </si>
   <si>
+    <t>116.5</t>
+  </si>
+  <si>
+    <t>5548.0</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>55.5</t>
+  </si>
+  <si>
+    <t>19일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>19일</t>
   </si>
   <si>
     <t>20일</t>
@@ -980,13 +992,13 @@
         <v>91</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -994,19 +1006,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1014,19 +1026,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1034,19 +1046,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1054,19 +1066,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1074,19 +1086,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1094,19 +1106,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1114,19 +1126,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1134,19 +1146,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1154,19 +1166,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1174,19 +1186,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1194,19 +1206,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1214,19 +1226,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1234,19 +1246,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="112">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>308.2</t>
+    <t>314.6</t>
   </si>
   <si>
     <t>-</t>
@@ -287,10 +287,10 @@
     <t>18일</t>
   </si>
   <si>
-    <t>116.5</t>
-  </si>
-  <si>
-    <t>5548.0</t>
+    <t>117.9</t>
+  </si>
+  <si>
+    <t>5549.4</t>
   </si>
   <si>
     <t>1.2</t>
@@ -302,10 +302,19 @@
     <t>19일</t>
   </si>
   <si>
+    <t>428.5</t>
+  </si>
+  <si>
+    <t>5977.9</t>
+  </si>
+  <si>
+    <t>59.8</t>
+  </si>
+  <si>
+    <t>20일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>20일</t>
   </si>
   <si>
     <t>21일</t>
@@ -1012,13 +1021,13 @@
         <v>96</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1026,19 +1035,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1046,19 +1055,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1066,19 +1075,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1086,19 +1095,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1106,19 +1115,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1126,19 +1135,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1146,19 +1155,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1166,19 +1175,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1186,19 +1195,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1206,19 +1215,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1226,19 +1235,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1246,19 +1255,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="116">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>314.6</t>
+    <t>305.3</t>
   </si>
   <si>
     <t>-</t>
@@ -302,10 +302,10 @@
     <t>19일</t>
   </si>
   <si>
-    <t>428.5</t>
-  </si>
-  <si>
-    <t>5977.9</t>
+    <t>430.0</t>
+  </si>
+  <si>
+    <t>5979.4</t>
   </si>
   <si>
     <t>59.8</t>
@@ -314,10 +314,22 @@
     <t>20일</t>
   </si>
   <si>
+    <t>127.3</t>
+  </si>
+  <si>
+    <t>6106.7</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>61.1</t>
+  </si>
+  <si>
+    <t>21일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>21일</t>
   </si>
   <si>
     <t>22일</t>
@@ -1041,13 +1053,13 @@
         <v>100</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1055,19 +1067,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1075,19 +1087,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1095,19 +1107,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1115,19 +1127,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1135,19 +1147,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1155,19 +1167,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1175,19 +1187,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1195,19 +1207,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1215,19 +1227,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1235,19 +1247,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1255,19 +1267,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="120">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>305.3</t>
+    <t>295.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.1</t>
+    <t>3.0</t>
   </si>
   <si>
     <t>01일</t>
@@ -329,10 +329,22 @@
     <t>21일</t>
   </si>
   <si>
+    <t>101.1</t>
+  </si>
+  <si>
+    <t>6207.8</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>62.1</t>
+  </si>
+  <si>
+    <t>22일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>22일</t>
   </si>
   <si>
     <t>23일</t>
@@ -1073,13 +1085,13 @@
         <v>105</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1087,19 +1099,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1107,19 +1119,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1127,19 +1139,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1147,19 +1159,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1167,19 +1179,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1187,19 +1199,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1207,19 +1219,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1227,19 +1239,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1247,19 +1259,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1267,19 +1279,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="124">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>295.6</t>
+    <t>290.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.0</t>
+    <t>2.9</t>
   </si>
   <si>
     <t>01일</t>
@@ -344,10 +344,22 @@
     <t>22일</t>
   </si>
   <si>
+    <t>174.6</t>
+  </si>
+  <si>
+    <t>6382.4</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>63.8</t>
+  </si>
+  <si>
+    <t>23일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>23일</t>
   </si>
   <si>
     <t>24일</t>
@@ -1105,13 +1117,13 @@
         <v>110</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1119,19 +1131,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1139,19 +1151,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1159,19 +1171,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1179,19 +1191,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1199,19 +1211,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1219,19 +1231,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1239,19 +1251,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1259,19 +1271,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1279,19 +1291,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="128">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>290.1</t>
+    <t>287.5</t>
   </si>
   <si>
     <t>-</t>
@@ -359,10 +359,22 @@
     <t>23일</t>
   </si>
   <si>
+    <t>229.5</t>
+  </si>
+  <si>
+    <t>6611.9</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>66.1</t>
+  </si>
+  <si>
+    <t>24일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>24일</t>
   </si>
   <si>
     <t>25일</t>
@@ -1137,13 +1149,13 @@
         <v>115</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1151,19 +1163,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1171,19 +1183,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1191,19 +1203,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1211,19 +1223,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1231,19 +1243,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1251,19 +1263,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1271,19 +1283,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1291,19 +1303,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="131">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>287.5</t>
+    <t>293.6</t>
   </si>
   <si>
     <t>-</t>
@@ -374,10 +374,19 @@
     <t>24일</t>
   </si>
   <si>
+    <t>434.2</t>
+  </si>
+  <si>
+    <t>7046.1</t>
+  </si>
+  <si>
+    <t>70.5</t>
+  </si>
+  <si>
+    <t>25일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>25일</t>
   </si>
   <si>
     <t>26일</t>
@@ -1169,13 +1178,13 @@
         <v>120</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1183,19 +1192,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1203,19 +1212,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1223,19 +1232,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1243,19 +1252,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1263,19 +1272,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1283,19 +1292,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1303,19 +1312,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="134">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>293.6</t>
+    <t>299.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>2.9</t>
+    <t>3.0</t>
   </si>
   <si>
     <t>01일</t>
@@ -374,10 +374,10 @@
     <t>24일</t>
   </si>
   <si>
-    <t>434.2</t>
-  </si>
-  <si>
-    <t>7046.1</t>
+    <t>434.5</t>
+  </si>
+  <si>
+    <t>7046.4</t>
   </si>
   <si>
     <t>70.5</t>
@@ -386,10 +386,19 @@
     <t>25일</t>
   </si>
   <si>
+    <t>428.8</t>
+  </si>
+  <si>
+    <t>7475.2</t>
+  </si>
+  <si>
+    <t>74.8</t>
+  </si>
+  <si>
+    <t>26일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>26일</t>
   </si>
   <si>
     <t>27일</t>
@@ -1198,13 +1207,13 @@
         <v>124</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>124</v>
+        <v>12</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1212,19 +1221,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1232,19 +1241,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1252,19 +1261,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1272,19 +1281,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1292,19 +1301,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1312,19 +1321,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="137">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>299.0</t>
+    <t>306.3</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.0</t>
+    <t>3.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -386,10 +386,10 @@
     <t>25일</t>
   </si>
   <si>
-    <t>428.8</t>
-  </si>
-  <si>
-    <t>7475.2</t>
+    <t>432.5</t>
+  </si>
+  <si>
+    <t>7478.9</t>
   </si>
   <si>
     <t>74.8</t>
@@ -398,10 +398,19 @@
     <t>26일</t>
   </si>
   <si>
+    <t>483.6</t>
+  </si>
+  <si>
+    <t>7962.5</t>
+  </si>
+  <si>
+    <t>79.6</t>
+  </si>
+  <si>
+    <t>27일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>27일</t>
   </si>
   <si>
     <t>28일</t>
@@ -1227,13 +1236,13 @@
         <v>128</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1241,19 +1250,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1261,19 +1270,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1281,19 +1290,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1301,19 +1310,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1321,19 +1330,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="141">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>306.3</t>
+    <t>311.0</t>
   </si>
   <si>
     <t>-</t>
@@ -398,10 +398,13 @@
     <t>26일</t>
   </si>
   <si>
-    <t>483.6</t>
-  </si>
-  <si>
-    <t>7962.5</t>
+    <t>485.7</t>
+  </si>
+  <si>
+    <t>7964.6</t>
+  </si>
+  <si>
+    <t>4.9</t>
   </si>
   <si>
     <t>79.6</t>
@@ -410,10 +413,19 @@
     <t>27일</t>
   </si>
   <si>
+    <t>433.3</t>
+  </si>
+  <si>
+    <t>8397.9</t>
+  </si>
+  <si>
+    <t>84.0</t>
+  </si>
+  <si>
+    <t>28일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>28일</t>
   </si>
   <si>
     <t>29일</t>
@@ -1239,10 +1251,10 @@
         <v>129</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1250,19 +1262,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1270,19 +1282,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1290,19 +1302,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1310,19 +1322,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1330,19 +1342,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="145">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>311.0</t>
+    <t>313.6</t>
   </si>
   <si>
     <t>-</t>
@@ -425,10 +425,22 @@
     <t>28일</t>
   </si>
   <si>
+    <t>382.6</t>
+  </si>
+  <si>
+    <t>8780.5</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>87.8</t>
+  </si>
+  <si>
+    <t>29일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>29일</t>
   </si>
   <si>
     <t>30일</t>
@@ -1288,13 +1300,13 @@
         <v>137</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1302,19 +1314,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1322,19 +1334,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1342,19 +1354,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="149">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>313.6</t>
+    <t>317.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.1</t>
+    <t>3.2</t>
   </si>
   <si>
     <t>01일</t>
@@ -440,10 +440,22 @@
     <t>29일</t>
   </si>
   <si>
+    <t>440.0</t>
+  </si>
+  <si>
+    <t>9220.5</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>92.2</t>
+  </si>
+  <si>
+    <t>30일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>30일</t>
   </si>
   <si>
     <t>31일</t>
@@ -1320,13 +1332,13 @@
         <v>142</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1334,19 +1346,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1354,19 +1366,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="152">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>317.9</t>
+    <t>320.4</t>
   </si>
   <si>
     <t>-</t>
@@ -455,10 +455,19 @@
     <t>30일</t>
   </si>
   <si>
+    <t>390.1</t>
+  </si>
+  <si>
+    <t>9610.6</t>
+  </si>
+  <si>
+    <t>96.1</t>
+  </si>
+  <si>
+    <t>31일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>31일</t>
   </si>
 </sst>
 </file>
@@ -1352,13 +1361,13 @@
         <v>147</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>147</v>
+        <v>40</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1366,19 +1375,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-07-01.xlsx
+++ b/past_data/site_8023/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="154">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>320.4</t>
+    <t>324.1</t>
   </si>
   <si>
     <t>-</t>
@@ -455,10 +455,10 @@
     <t>30일</t>
   </si>
   <si>
-    <t>390.1</t>
-  </si>
-  <si>
-    <t>9610.6</t>
+    <t>390.2</t>
+  </si>
+  <si>
+    <t>9610.7</t>
   </si>
   <si>
     <t>96.1</t>
@@ -467,7 +467,13 @@
     <t>31일</t>
   </si>
   <si>
-    <t>0.0</t>
+    <t>435.4</t>
+  </si>
+  <si>
+    <t>10046.1</t>
+  </si>
+  <si>
+    <t>100.5</t>
   </si>
 </sst>
 </file>
@@ -1381,13 +1387,13 @@
         <v>151</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
